--- a/public/modelo-importacao-organograma.xlsx
+++ b/public/modelo-importacao-organograma.xlsx
@@ -398,19 +398,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:R6"/>
   <cols>
-    <col min="1" max="1" width="42.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
     <col min="10" max="10" width="20.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="17" max="17" width="20.83203125" customWidth="1"/>
+    <col min="18" max="18" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -424,28 +431,49 @@
         <v>Nome Colaborador</v>
       </c>
       <c r="D1" t="str">
+        <v>Tipo Contratação</v>
+      </c>
+      <c r="E1" t="str">
         <v>Cargo</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Setor</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>Codigo Setor</v>
+      </c>
+      <c r="H1" t="str">
         <v>Cod. Cargo</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Cod. Nivel Hierar. Cargo</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
+        <v>Variação Nivel Cargo</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Familia Nível Cargo</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Cod. Nivel Hierarquia</v>
+      </c>
+      <c r="M1" t="str">
         <v>Matricula Lider</v>
       </c>
-      <c r="I1" t="str">
+      <c r="N1" t="str">
         <v>Nome Lider</v>
       </c>
-      <c r="J1" t="str">
+      <c r="O1" t="str">
         <v>Situação Colaborador</v>
       </c>
-      <c r="K1" t="str">
+      <c r="P1" t="str">
+        <v>Codigo Situação Colaborador</v>
+      </c>
+      <c r="Q1" t="str">
         <v>Local de Trabalho</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Cod. Local Trabalho</v>
       </c>
     </row>
     <row r="2">
@@ -453,34 +481,55 @@
         <v>010200</v>
       </c>
       <c r="B2" t="str">
-        <v>Juiz de Fora</v>
+        <v>Juiz De Fora</v>
       </c>
       <c r="C2" t="str">
         <v>Ana Paula Ribeiro</v>
       </c>
       <c r="D2" t="str">
+        <v>CLT</v>
+      </c>
+      <c r="E2" t="str">
         <v>Gerente Corporativo de TI</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="F2" t="str">
-        <v>C100</v>
-      </c>
       <c r="G2" t="str">
+        <v>SET304</v>
+      </c>
+      <c r="H2" t="str">
+        <v>89</v>
+      </c>
+      <c r="I2" t="str">
+        <v>6</v>
+      </c>
+      <c r="J2" t="str">
+        <v>6.A</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Gerente</v>
+      </c>
+      <c r="L2" t="str">
+        <v>NH505</v>
+      </c>
+      <c r="M2" t="str">
         <v/>
       </c>
-      <c r="H2" t="str">
+      <c r="N2" t="str">
         <v/>
       </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
+      <c r="O2" t="str">
         <v>Ativo</v>
       </c>
-      <c r="K2" t="str">
-        <v>Rossi - TI</v>
+      <c r="P2" t="str">
+        <v>A</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Rossi - Administrativo Backoffice</v>
+      </c>
+      <c r="R2" t="str">
+        <v>LOCTRA207</v>
       </c>
     </row>
     <row r="3">
@@ -488,34 +537,55 @@
         <v>010333</v>
       </c>
       <c r="B3" t="str">
-        <v>Juiz de Fora</v>
+        <v>Juiz De Fora</v>
       </c>
       <c r="C3" t="str">
         <v>Flavio de Paulo Maurilio</v>
       </c>
       <c r="D3" t="str">
+        <v>CLT</v>
+      </c>
+      <c r="E3" t="str">
         <v>Analista de Infraestrutura</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="F3" t="str">
-        <v>C201</v>
-      </c>
       <c r="G3" t="str">
-        <v/>
+        <v>SET304</v>
       </c>
       <c r="H3" t="str">
+        <v>16</v>
+      </c>
+      <c r="I3" t="str">
+        <v>12</v>
+      </c>
+      <c r="J3" t="str">
+        <v>12.A</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Analista</v>
+      </c>
+      <c r="L3" t="str">
+        <v>NH518</v>
+      </c>
+      <c r="M3" t="str">
         <v>010200</v>
       </c>
-      <c r="I3" t="str">
+      <c r="N3" t="str">
         <v>Ana Paula Ribeiro</v>
       </c>
-      <c r="J3" t="str">
+      <c r="O3" t="str">
         <v>Ativo</v>
       </c>
-      <c r="K3" t="str">
-        <v>Rossi - TI</v>
+      <c r="P3" t="str">
+        <v>A</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Rossi - Administrativo Backoffice</v>
+      </c>
+      <c r="R3" t="str">
+        <v>LOCTRA207</v>
       </c>
     </row>
     <row r="4">
@@ -523,34 +593,55 @@
         <v>014381</v>
       </c>
       <c r="B4" t="str">
-        <v>Juiz de Fora</v>
+        <v>Juiz De Fora</v>
       </c>
       <c r="C4" t="str">
         <v>Igor Demolinari Neiva</v>
       </c>
       <c r="D4" t="str">
+        <v>CLT</v>
+      </c>
+      <c r="E4" t="str">
         <v>Analista de Sistemas</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="F4" t="str">
-        <v>C202</v>
-      </c>
       <c r="G4" t="str">
-        <v/>
+        <v>SET304</v>
       </c>
       <c r="H4" t="str">
+        <v>24</v>
+      </c>
+      <c r="I4" t="str">
+        <v>12</v>
+      </c>
+      <c r="J4" t="str">
+        <v>12.A</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Analista</v>
+      </c>
+      <c r="L4" t="str">
+        <v>NH518</v>
+      </c>
+      <c r="M4" t="str">
         <v>010200</v>
       </c>
-      <c r="I4" t="str">
+      <c r="N4" t="str">
         <v>Ana Paula Ribeiro</v>
       </c>
-      <c r="J4" t="str">
+      <c r="O4" t="str">
         <v>Férias</v>
       </c>
-      <c r="K4" t="str">
-        <v>Rossi - TI</v>
+      <c r="P4" t="str">
+        <v>F</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Rossi - Administrativo Backoffice</v>
+      </c>
+      <c r="R4" t="str">
+        <v>LOCTRA207</v>
       </c>
     </row>
     <row r="5">
@@ -558,120 +649,127 @@
         <v>016086</v>
       </c>
       <c r="B5" t="str">
-        <v>Juiz de Fora</v>
+        <v>Juiz De Fora</v>
       </c>
       <c r="C5" t="str">
         <v>Fabiano Camara Titoneli</v>
       </c>
       <c r="D5" t="str">
-        <v>Estagiario T.I</v>
+        <v>CLT</v>
       </c>
       <c r="E5" t="str">
+        <v>Estagiário de TI</v>
+      </c>
+      <c r="F5" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="F5" t="str">
-        <v>C900</v>
-      </c>
       <c r="G5" t="str">
-        <v/>
+        <v>SET304</v>
       </c>
       <c r="H5" t="str">
+        <v>145</v>
+      </c>
+      <c r="I5" t="str">
+        <v>16</v>
+      </c>
+      <c r="J5" t="str">
+        <v>16.A</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Estagiário</v>
+      </c>
+      <c r="L5" t="str">
+        <v>NH541</v>
+      </c>
+      <c r="M5" t="str">
         <v>010333</v>
       </c>
-      <c r="I5" t="str">
+      <c r="N5" t="str">
         <v>Flavio de Paulo Maurilio</v>
       </c>
-      <c r="J5" t="str">
+      <c r="O5" t="str">
         <v>Ativo</v>
       </c>
-      <c r="K5" t="str">
-        <v>Rossi - Administrativo</v>
+      <c r="P5" t="str">
+        <v>A</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Rossi - Administrativo Backoffice</v>
+      </c>
+      <c r="R5" t="str">
+        <v>LOCTRA207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>015639</v>
+        <v>PJ1023</v>
       </c>
       <c r="B6" t="str">
-        <v>Juiz de Fora</v>
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>Lucas Moreira Abreu</v>
+        <v>Raphael Soares Moreira</v>
       </c>
       <c r="D6" t="str">
-        <v>Aprendiz</v>
+        <v>PJ</v>
       </c>
       <c r="E6" t="str">
+        <v>Desenvolvedor de Sistemas</v>
+      </c>
+      <c r="F6" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="F6" t="str">
-        <v>C950</v>
-      </c>
       <c r="G6" t="str">
-        <v/>
+        <v>SET304</v>
       </c>
       <c r="H6" t="str">
-        <v>010333</v>
+        <v>PJUR120</v>
       </c>
       <c r="I6" t="str">
-        <v>Flavio de Paulo Maurilio</v>
+        <v>11</v>
       </c>
       <c r="J6" t="str">
+        <v>11.C</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Desenvolvedor</v>
+      </c>
+      <c r="L6" t="str">
+        <v>NH515</v>
+      </c>
+      <c r="M6" t="str">
+        <v>010200</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Ana Paula Ribeiro</v>
+      </c>
+      <c r="O6" t="str">
         <v>Ativo</v>
       </c>
-      <c r="K6" t="str">
-        <v>Rossi - Administrativo</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>PJ1023</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v>Raphael Soares Moreira</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v>Tecnologia da Informação</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v>010200</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Ana Paula Ribeiro</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Ativo</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Tecnologia da Informação</v>
+      <c r="P6" t="str">
+        <v>A</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Rossi - Administrativo Backoffice</v>
+      </c>
+      <c r="R6" t="str">
+        <v>LOCTRA207</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C13"/>
   <cols>
-    <col min="1" max="1" width="44.83203125" customWidth="1"/>
+    <col min="1" max="1" width="48.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="90.83203125" customWidth="1"/>
+    <col min="3" max="3" width="80.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -693,7 +791,7 @@
         <v>SIM</v>
       </c>
       <c r="C2" t="str">
-        <v>Matrícula/chapa única. PJ usa prefixo 'PJ' (ex.: PJ1023) → o sistema marca como PJ.</v>
+        <v>Matrícula única (chapa). PJ pode usar prefixo PJ.</v>
       </c>
     </row>
     <row r="3">
@@ -709,172 +807,117 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Cargo</v>
+        <v>Tipo Contratação</v>
       </c>
       <c r="B4" t="str">
         <v>recomendado</v>
       </c>
       <c r="C4" t="str">
-        <v>Texto do cargo. Se não existir na lista, é criado automaticamente.</v>
+        <v>CLT ou PJ (se vazio, o sistema infere pelo prefixo da matrícula).</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Setor</v>
+        <v>Cargo</v>
       </c>
       <c r="B5" t="str">
         <v>recomendado</v>
       </c>
       <c r="C5" t="str">
-        <v>Área/setor. Se não existir, é criado automaticamente.</v>
+        <v>Nome do cargo. Casado com o catálogo; criado se novo.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Matricula Lider</v>
+        <v>Codigo Setor</v>
       </c>
       <c r="B6" t="str">
         <v>recomendado</v>
       </c>
       <c r="C6" t="str">
-        <v>MATRÍCULA do líder direto (não o nome). Em branco = topo da área (raiz).</v>
+        <v>Código oficial do setor (SET…). Usado para casar a área com precisão.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Situação Colaborador</v>
+        <v>Setor</v>
       </c>
       <c r="B7" t="str">
         <v>recomendado</v>
       </c>
       <c r="C7" t="str">
-        <v>Deve ser uma situação válida (Ativo, Afastado, Férias, Aviso Prévio, Af. Previdência, Licença, Licença Maternidade, Inativo, Desligado). Desligado/Inativo não aparecem no organograma.</v>
+        <v>Nome da área (usado se não houver código).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Local de Trabalho</v>
+        <v>Cod. Nivel Hierarquia</v>
       </c>
       <c r="B8" t="str">
         <v>opcional</v>
       </c>
       <c r="C8" t="str">
-        <v>Filial/unidade. Criado automaticamente se novo.</v>
+        <v>NH… — define o nível de um cargo NOVO. Cargos já cadastrados mantêm o nível.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Regional</v>
+        <v>Matricula Lider</v>
       </c>
       <c r="B9" t="str">
-        <v>opcional</v>
+        <v>recomendado</v>
       </c>
       <c r="C9" t="str">
-        <v>Cidade/região.</v>
+        <v>MATRÍCULA do líder direto (não o nome). Vazio = topo da área.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Cod. Cargo</v>
+        <v>Situação Colaborador / Codigo Situação</v>
       </c>
       <c r="B10" t="str">
-        <v>opcional</v>
+        <v>recomendado</v>
       </c>
       <c r="C10" t="str">
-        <v>Código do cargo no DP (referência).</v>
+        <v>Situação (nome) e/ou código-letra (A,F,V,P…). Deve existir na lista do banco.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Nome Lider</v>
+        <v>Local de Trabalho / Cod. Local Trabalho</v>
       </c>
       <c r="B11" t="str">
-        <v>IGNORADO</v>
+        <v>opcional</v>
       </c>
       <c r="C11" t="str">
-        <v>Derivado pela matrícula do líder — não precisa preencher.</v>
+        <v>Local e código (LOCTRA…).</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Cod. Nivel Hierar. Cargo</v>
+        <v>Regional</v>
       </c>
       <c r="B12" t="str">
-        <v>IGNORADO</v>
+        <v>opcional</v>
       </c>
       <c r="C12" t="str">
-        <v>Não é usado (a base oficial traz valores inconsistentes).</v>
+        <v>Cidade/região.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Nome Lider / Cod. Cargo / Cod. Nivel Hierar. Cargo / Variação / Familia</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>IGNORADO</v>
       </c>
       <c r="C13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Regras da importação:</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v/>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v>Upsert por matrícula: quem já existe é atualizado, quem é novo é inserido.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v/>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v>Quem está no banco mas NÃO vier no arquivo é ARQUIVADO (some do organograma, fica no histórico). Nada é apagado.</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v/>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v>Linhas com erro (matrícula duplicada/vazia, situação inválida) são puladas; as válidas entram.</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v/>
-      </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v>Líder inexistente ou ciclo: a pessoa entra sem líder e fica marcada como inconsistência.</v>
+        <v>Não são usados na importação (derivados ou redundantes).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/modelo-importacao-organograma.xlsx
+++ b/public/modelo-importacao-organograma.xlsx
@@ -398,26 +398,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:S6"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="24.83203125" customWidth="1"/>
     <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="12" max="12" width="19.83203125" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
     <col min="16" max="16" width="20.83203125" customWidth="1"/>
-    <col min="17" max="17" width="20.83203125" customWidth="1"/>
-    <col min="18" max="18" width="20.83203125" customWidth="1"/>
+    <col min="17" max="17" width="27.83203125" customWidth="1"/>
+    <col min="18" max="18" width="17.83203125" customWidth="1"/>
+    <col min="19" max="19" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -431,48 +432,51 @@
         <v>Nome Colaborador</v>
       </c>
       <c r="D1" t="str">
+        <v>CPF</v>
+      </c>
+      <c r="E1" t="str">
         <v>Tipo Contratação</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Cargo</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Setor</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Codigo Setor</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Cod. Cargo</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Cod. Nivel Hierar. Cargo</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Variação Nivel Cargo</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Familia Nível Cargo</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Cod. Nivel Hierarquia</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Matricula Lider</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Nome Lider</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Situação Colaborador</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Codigo Situação Colaborador</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Local de Trabalho</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Cod. Local Trabalho</v>
       </c>
     </row>
@@ -487,48 +491,51 @@
         <v>Ana Paula Ribeiro</v>
       </c>
       <c r="D2" t="str">
+        <v>123.456.789-00</v>
+      </c>
+      <c r="E2" t="str">
         <v>CLT</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Gerente Corporativo de TI</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>SET304</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>89</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>6</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>6.A</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Gerente</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>NH505</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
       </c>
       <c r="N2" t="str">
         <v/>
       </c>
       <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
         <v>Ativo</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>A</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>Rossi - Administrativo Backoffice</v>
       </c>
-      <c r="R2" t="str">
+      <c r="S2" t="str">
         <v>LOCTRA207</v>
       </c>
     </row>
@@ -543,48 +550,51 @@
         <v>Flavio de Paulo Maurilio</v>
       </c>
       <c r="D3" t="str">
+        <v>987.654.321-00</v>
+      </c>
+      <c r="E3" t="str">
         <v>CLT</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Analista de Infraestrutura</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>SET304</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>16</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>12</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>12.A</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>Analista</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>NH518</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>010200</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>Ana Paula Ribeiro</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>Ativo</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>A</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>Rossi - Administrativo Backoffice</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
         <v>LOCTRA207</v>
       </c>
     </row>
@@ -599,48 +609,51 @@
         <v>Igor Demolinari Neiva</v>
       </c>
       <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
         <v>CLT</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>Analista de Sistemas</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>SET304</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>24</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>12</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>12.A</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>Analista</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>NH518</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>010200</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>Ana Paula Ribeiro</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>Férias</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>F</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="R4" t="str">
         <v>Rossi - Administrativo Backoffice</v>
       </c>
-      <c r="R4" t="str">
+      <c r="S4" t="str">
         <v>LOCTRA207</v>
       </c>
     </row>
@@ -655,48 +668,51 @@
         <v>Fabiano Camara Titoneli</v>
       </c>
       <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
         <v>CLT</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>Estagiário de TI</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>SET304</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>145</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>16</v>
       </c>
-      <c r="J5" t="str">
+      <c r="K5" t="str">
         <v>16.A</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <v>Estagiário</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>NH541</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>010333</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>Flavio de Paulo Maurilio</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>Ativo</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>A</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="R5" t="str">
         <v>Rossi - Administrativo Backoffice</v>
       </c>
-      <c r="R5" t="str">
+      <c r="S5" t="str">
         <v>LOCTRA207</v>
       </c>
     </row>
@@ -711,65 +727,68 @@
         <v>Raphael Soares Moreira</v>
       </c>
       <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
         <v>PJ</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>Desenvolvedor de Sistemas</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>Tecnologia da Informação</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>SET304</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>PJUR120</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>11</v>
       </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
         <v>11.C</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>Desenvolvedor</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>NH515</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>010200</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>Ana Paula Ribeiro</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>Ativo</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <v>A</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="R6" t="str">
         <v>Rossi - Administrativo Backoffice</v>
       </c>
-      <c r="R6" t="str">
+      <c r="S6" t="str">
         <v>LOCTRA207</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <cols>
-    <col min="1" max="1" width="48.83203125" customWidth="1"/>
+    <col min="1" max="1" width="44.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="80.83203125" customWidth="1"/>
+    <col min="3" max="3" width="88.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -807,117 +826,128 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Tipo Contratação</v>
+        <v>CPF</v>
       </c>
       <c r="B4" t="str">
-        <v>recomendado</v>
+        <v>opcional</v>
       </c>
       <c r="C4" t="str">
-        <v>CLT ou PJ (se vazio, o sistema infere pelo prefixo da matrícula).</v>
+        <v>CPF do colaborador (com ou sem pontuação). Vazio não bloqueia a importação; quando vem, atualiza o cadastro.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Cargo</v>
+        <v>Tipo Contratação</v>
       </c>
       <c r="B5" t="str">
         <v>recomendado</v>
       </c>
       <c r="C5" t="str">
-        <v>Nome do cargo. Casado com o catálogo; criado se novo.</v>
+        <v>CLT ou PJ (se vazio, o sistema infere pelo prefixo da matrícula).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Codigo Setor</v>
+        <v>Cargo</v>
       </c>
       <c r="B6" t="str">
         <v>recomendado</v>
       </c>
       <c r="C6" t="str">
-        <v>Código oficial do setor (SET…). Usado para casar a área com precisão.</v>
+        <v>Nome do cargo. Casado com o catálogo; criado se novo.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Setor</v>
+        <v>Codigo Setor</v>
       </c>
       <c r="B7" t="str">
         <v>recomendado</v>
       </c>
       <c r="C7" t="str">
-        <v>Nome da área (usado se não houver código).</v>
+        <v>Código oficial do setor (SET…). Usado para casar a área com precisão.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Cod. Nivel Hierarquia</v>
+        <v>Setor</v>
       </c>
       <c r="B8" t="str">
-        <v>opcional</v>
+        <v>recomendado</v>
       </c>
       <c r="C8" t="str">
-        <v>NH… — define o nível de um cargo NOVO. Cargos já cadastrados mantêm o nível.</v>
+        <v>Nome da área (usado se não houver código).</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Matricula Lider</v>
+        <v>Cod. Nivel Hierarquia</v>
       </c>
       <c r="B9" t="str">
-        <v>recomendado</v>
+        <v>opcional</v>
       </c>
       <c r="C9" t="str">
-        <v>MATRÍCULA do líder direto (não o nome). Vazio = topo da área.</v>
+        <v>NH… — define o nível de um cargo NOVO. Cargos já cadastrados mantêm o nível.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Situação Colaborador / Codigo Situação</v>
+        <v>Matricula Lider</v>
       </c>
       <c r="B10" t="str">
         <v>recomendado</v>
       </c>
       <c r="C10" t="str">
-        <v>Situação (nome) e/ou código-letra (A,F,V,P…). Deve existir na lista do banco.</v>
+        <v>MATRÍCULA do líder direto (não o nome). Vazio = topo da área.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Local de Trabalho / Cod. Local Trabalho</v>
+        <v>Situação Colaborador / Codigo Situação</v>
       </c>
       <c r="B11" t="str">
-        <v>opcional</v>
+        <v>recomendado</v>
       </c>
       <c r="C11" t="str">
-        <v>Local e código (LOCTRA…).</v>
+        <v>Situação (nome) e/ou código-letra (A,F,V,P…). Deve existir na lista do banco.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Regional</v>
+        <v>Local de Trabalho / Cod. Local Trabalho</v>
       </c>
       <c r="B12" t="str">
         <v>opcional</v>
       </c>
       <c r="C12" t="str">
-        <v>Cidade/região.</v>
+        <v>Local e código (LOCTRA…).</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>Regional</v>
+      </c>
+      <c r="B13" t="str">
+        <v>opcional</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Cidade/região.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
         <v>Nome Lider / Cod. Cargo / Cod. Nivel Hierar. Cargo / Variação / Familia</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B14" t="str">
         <v>IGNORADO</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C14" t="str">
         <v>Não são usados na importação (derivados ou redundantes).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
   </ignoredErrors>
 </worksheet>
 </file>